--- a/testScenario/Lereve Manual Testing.xlsx
+++ b/testScenario/Lereve Manual Testing.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>Please click here to see the full  pdf</t>
   </si>
@@ -56,10 +56,61 @@
     <t>TS-01</t>
   </si>
   <si>
-    <t xml:space="preserve">Header </t>
+    <t>Header</t>
+  </si>
+  <si>
+    <t>Verify header UI, alignment, logo, icons visibility across all pages.</t>
   </si>
   <si>
     <t>TS-02</t>
+  </si>
+  <si>
+    <t>Header Navigation</t>
+  </si>
+  <si>
+    <t>Verify all menu links (Summer, Women, Men, etc.) redirect to correct pages.</t>
+  </si>
+  <si>
+    <t>Login</t>
+  </si>
+  <si>
+    <t>Verify login using phone.</t>
+  </si>
+  <si>
+    <t>Hero Banner UI</t>
+  </si>
+  <si>
+    <t>Verify banner image, text colors  and font sizes.</t>
+  </si>
+  <si>
+    <t>Banner Navigation</t>
+  </si>
+  <si>
+    <t>Verify clicking "Casual Summer" text and "Shop This Style" button redirects to Summer Collection.</t>
+  </si>
+  <si>
+    <t>Carousel Slider</t>
+  </si>
+  <si>
+    <t>Verify the slider dots on the right allow switching between banners.</t>
+  </si>
+  <si>
+    <t>Search</t>
+  </si>
+  <si>
+    <t>Verify search functionality including keyword search, suggestions, pagination, and accessibility</t>
+  </si>
+  <si>
+    <t>Cart</t>
+  </si>
+  <si>
+    <t>Verify cart functionality including item management, pricing, coupons, and restrictions</t>
+  </si>
+  <si>
+    <t>Contact Us</t>
+  </si>
+  <si>
+    <t>Verify contact us page UI, form validation, submission, and link redirections</t>
   </si>
   <si>
     <t>t</t>
@@ -72,7 +123,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="9">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -98,8 +149,24 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
+      <name val="System-ui"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -110,6 +177,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF0B5394"/>
         <bgColor rgb="FF0B5394"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor theme="0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7F8FC"/>
+        <bgColor rgb="FFF7F8FC"/>
       </patternFill>
     </fill>
   </fills>
@@ -149,7 +228,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -175,6 +254,18 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -460,7 +551,7 @@
   <cols>
     <col customWidth="1" min="1" max="1" width="14.0"/>
     <col customWidth="1" min="2" max="2" width="16.38"/>
-    <col customWidth="1" min="3" max="3" width="50.88"/>
+    <col customWidth="1" min="3" max="3" width="78.38"/>
     <col customWidth="1" min="4" max="4" width="25.13"/>
   </cols>
   <sheetData>
@@ -525,10 +616,75 @@
       <c r="B9" s="9" t="s">
         <v>13</v>
       </c>
+      <c r="C9" s="10" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -565,7 +721,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/testScenario/Lereve Manual Testing.xlsx
+++ b/testScenario/Lereve Manual Testing.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="131">
   <si>
     <t>Please click here to see the full  pdf</t>
   </si>
@@ -71,46 +71,369 @@
     <t>Verify all menu links (Summer, Women, Men, etc.) redirect to correct pages.</t>
   </si>
   <si>
+    <t>TS-03</t>
+  </si>
+  <si>
     <t>Login</t>
   </si>
   <si>
     <t>Verify login using phone.</t>
   </si>
   <si>
+    <t>TS-04</t>
+  </si>
+  <si>
     <t>Hero Banner UI</t>
   </si>
   <si>
     <t>Verify banner image, text colors  and font sizes.</t>
   </si>
   <si>
+    <t>TS-05</t>
+  </si>
+  <si>
     <t>Banner Navigation</t>
   </si>
   <si>
     <t>Verify clicking "Casual Summer" text and "Shop This Style" button redirects to Summer Collection.</t>
   </si>
   <si>
+    <t>TS-06</t>
+  </si>
+  <si>
     <t>Carousel Slider</t>
   </si>
   <si>
     <t>Verify the slider dots on the right allow switching between banners.</t>
   </si>
   <si>
+    <t>TS-07</t>
+  </si>
+  <si>
     <t>Search</t>
   </si>
   <si>
     <t>Verify search functionality including keyword search, suggestions, pagination, and accessibility</t>
   </si>
   <si>
+    <t>TS-08</t>
+  </si>
+  <si>
     <t>Cart</t>
   </si>
   <si>
     <t>Verify cart functionality including item management, pricing, coupons, and restrictions</t>
   </si>
   <si>
+    <t>TS-09</t>
+  </si>
+  <si>
     <t>Contact Us</t>
   </si>
   <si>
     <t>Verify contact us page UI, form validation, submission, and link redirections</t>
+  </si>
+  <si>
+    <t>TS-10</t>
+  </si>
+  <si>
+    <t>Categories</t>
+  </si>
+  <si>
+    <t>Verify Category Navigation, Dropdown Menu, and Product Filtering Functionality</t>
+  </si>
+  <si>
+    <t>Product Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC Start Date </t>
+  </si>
+  <si>
+    <t>Executed By</t>
+  </si>
+  <si>
+    <t>#SL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type of Testing </t>
+  </si>
+  <si>
+    <t>Features</t>
+  </si>
+  <si>
+    <t>Test Cases</t>
+  </si>
+  <si>
+    <t>Expected Result</t>
+  </si>
+  <si>
+    <t>Actual Result</t>
+  </si>
+  <si>
+    <t>Reproducing Steps</t>
+  </si>
+  <si>
+    <t>Bugs scrrenshot</t>
+  </si>
+  <si>
+    <t>Final Status</t>
+  </si>
+  <si>
+    <t>Header Module</t>
+  </si>
+  <si>
+    <t>UI Testing</t>
+  </si>
+  <si>
+    <t>Header Section</t>
+  </si>
+  <si>
+    <t>Verify header section is displayed on the website</t>
+  </si>
+  <si>
+    <t>Header should be visible on page load</t>
+  </si>
+  <si>
+    <t>Found as per as expectation</t>
+  </si>
+  <si>
+    <t>1. Open lereve URL .   
+2. Open Homepage</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>Header
+ Alignment</t>
+  </si>
+  <si>
+    <t>Logo Alignment</t>
+  </si>
+  <si>
+    <t>Header 
+Consistency</t>
+  </si>
+  <si>
+    <t>Icons &amp; Text</t>
+  </si>
+  <si>
+    <t>Dropdown Menu</t>
+  </si>
+  <si>
+    <t>Not found as per as 
+expectation</t>
+  </si>
+  <si>
+    <t>Functional 
+Testing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Header Links
+</t>
+  </si>
+  <si>
+    <t>Navigation</t>
+  </si>
+  <si>
+    <t>Logo Navigation</t>
+  </si>
+  <si>
+    <t>Search Bar</t>
+  </si>
+  <si>
+    <t>Search Module</t>
+  </si>
+  <si>
+    <t>Search Field</t>
+  </si>
+  <si>
+    <t>Verify spelling and grammar 
+of placeholder</t>
+  </si>
+  <si>
+    <t>Text should be correct</t>
+  </si>
+  <si>
+    <t>Found as per as expectations</t>
+  </si>
+  <si>
+    <t>Open Page</t>
+  </si>
+  <si>
+    <t>Search Icon</t>
+  </si>
+  <si>
+    <t>Verify search with valid 
+keyword</t>
+  </si>
+  <si>
+    <t>Verify search using Enter key</t>
+  </si>
+  <si>
+    <t>Pagination</t>
+  </si>
+  <si>
+    <t>Verify pagination appears</t>
+  </si>
+  <si>
+    <t>Search Results</t>
+  </si>
+  <si>
+    <t>Verify related keywords 
+shown</t>
+  </si>
+  <si>
+    <t>Footer</t>
+  </si>
+  <si>
+    <t>Footer Alignment</t>
+  </si>
+  <si>
+    <t>Verify footer section 
+alignment</t>
+  </si>
+  <si>
+    <t>Footer 
+Consistency</t>
+  </si>
+  <si>
+    <t>Verify same footer appears 
+on all pages</t>
+  </si>
+  <si>
+    <t>Follow Us Section</t>
+  </si>
+  <si>
+    <t>Verify correctness of social 
+media icons in Follow Us 
+section</t>
+  </si>
+  <si>
+    <t>Copyright</t>
+  </si>
+  <si>
+    <t>Verify year &amp; icon displayed</t>
+  </si>
+  <si>
+    <t>Footer Links</t>
+  </si>
+  <si>
+    <t>Verify all footer links are click-
+-able</t>
+  </si>
+  <si>
+    <t>Verify correct page opens on 
+clicking header links</t>
+  </si>
+  <si>
+    <t>Social Links</t>
+  </si>
+  <si>
+    <t>Verify social icons redirect 
+correctly</t>
+  </si>
+  <si>
+    <t>Login Module</t>
+  </si>
+  <si>
+    <t>Placeholder</t>
+  </si>
+  <si>
+    <t>Verify placeholder text in fields</t>
+  </si>
+  <si>
+    <t>Post Login UI</t>
+  </si>
+  <si>
+    <t>Verify Sign Up not shown after 
+login</t>
+  </si>
+  <si>
+    <t>Spelling</t>
+  </si>
+  <si>
+    <t>Verify spelling mistakes</t>
+  </si>
+  <si>
+    <t>Login Page</t>
+  </si>
+  <si>
+    <t>Verify login page loads properly</t>
+  </si>
+  <si>
+    <t>Valid Login</t>
+  </si>
+  <si>
+    <t>Verify login with valid phone
+number and OTP</t>
+  </si>
+  <si>
+    <t>Invalid Login</t>
+  </si>
+  <si>
+    <t>Verify error message for invalid
+phone number</t>
+  </si>
+  <si>
+    <t>Verify error message for invalid
+OTP</t>
+  </si>
+  <si>
+    <t>Keyboard</t>
+  </si>
+  <si>
+    <t>Verify login using Enter key</t>
+  </si>
+  <si>
+    <t>Categories Module (https://www.lerevecraze.com/product-category)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UI Testing </t>
+  </si>
+  <si>
+    <t>Category Text</t>
+  </si>
+  <si>
+    <t>Verify category names are 
+spelled correctly</t>
+  </si>
+  <si>
+    <t>Category Hover</t>
+  </si>
+  <si>
+    <t>Verify dropdown appears on 
+hover for each category</t>
+  </si>
+  <si>
+    <t>Category Click</t>
+  </si>
+  <si>
+    <t>Verify clicking on category 
+navigates to category page</t>
+  </si>
+  <si>
+    <t>Dropdown Display</t>
+  </si>
+  <si>
+    <t>Verify subcategories are 
+displayed in dropdown</t>
+  </si>
+  <si>
+    <t>Product Sorting</t>
+  </si>
+  <si>
+    <t>Verify products can be sorted 
+correctly using all available 
+sorting options</t>
+  </si>
+  <si>
+    <t>Product Filtering</t>
+  </si>
+  <si>
+    <t>Verify products can be filtered 
+correctly using all available 
+filter options</t>
   </si>
   <si>
     <t>t</t>
@@ -123,7 +446,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="14">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -165,8 +488,37 @@
       <color rgb="FF000000"/>
       <name val="System-ui"/>
     </font>
+    <font>
+      <u/>
+      <color rgb="FF0000FF"/>
+    </font>
+    <font>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12.0"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -191,9 +543,29 @@
         <bgColor rgb="FFF7F8FC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF38761D"/>
+        <bgColor rgb="FF38761D"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="6">
     <border/>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -224,54 +596,187 @@
         <color rgb="FF000000"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="34">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="3" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="2" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
+    <xf borderId="5" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="5">
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF356854"/>
+          <bgColor rgb="FF356854"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF6F8F9"/>
+          <bgColor rgb="FFF6F8F9"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF356854"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF356854"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF356854"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF356854"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="1">
+    <tableStyle count="4" pivot="0" name="test_scenario-style">
+      <tableStyleElement dxfId="1" type="headerRow"/>
+      <tableStyleElement dxfId="2" type="firstRowStripe"/>
+      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
+    </tableStyle>
+  </tableStyles>
 </styleSheet>
 </file>
 
@@ -326,6 +831,18 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A8:D18" displayName="Table1" name="Table1" id="1">
+  <tableColumns count="4">
+    <tableColumn name="Test Scenario ID" id="1"/>
+    <tableColumn name="Reference" id="2"/>
+    <tableColumn name="Test Scenario Description" id="3"/>
+    <tableColumn name="Number of Test Cases" id="4"/>
+  </tableColumns>
+  <tableStyleInfo name="test_scenario-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -549,9 +1066,9 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="14.0"/>
+    <col customWidth="1" min="1" max="1" width="17.63"/>
     <col customWidth="1" min="2" max="2" width="16.38"/>
-    <col customWidth="1" min="3" max="3" width="78.38"/>
+    <col customWidth="1" min="3" max="3" width="37.63"/>
     <col customWidth="1" min="4" max="4" width="25.13"/>
   </cols>
   <sheetData>
@@ -595,7 +1112,7 @@
       <c r="C5" s="4"/>
       <c r="D5" s="5"/>
     </row>
-    <row r="8">
+    <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="8" t="s">
         <v>8</v>
       </c>
@@ -609,7 +1126,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="9" t="s">
         <v>12</v>
       </c>
@@ -619,8 +1136,11 @@
       <c r="C9" s="10" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="10">
+      <c r="D9" s="9">
+        <v>15.0</v>
+      </c>
+    </row>
+    <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="9" t="s">
         <v>15</v>
       </c>
@@ -630,61 +1150,120 @@
       <c r="C10" s="11" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="11">
+      <c r="D10" s="9">
+        <v>26.0</v>
+      </c>
+    </row>
+    <row r="11" ht="22.5" customHeight="1">
+      <c r="A11" s="9" t="s">
+        <v>18</v>
+      </c>
       <c r="B11" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>20</v>
+      </c>
+      <c r="D11" s="9">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="12" ht="22.5" customHeight="1">
+      <c r="A12" s="9" t="s">
+        <v>21</v>
+      </c>
       <c r="B12" s="9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>23</v>
+      </c>
+      <c r="D12" s="9">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="13" ht="22.5" customHeight="1">
+      <c r="A13" s="9" t="s">
+        <v>24</v>
+      </c>
       <c r="B13" s="9" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>26</v>
+      </c>
+      <c r="D13" s="9">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="14" ht="22.5" customHeight="1">
+      <c r="A14" s="9" t="s">
+        <v>27</v>
+      </c>
       <c r="B14" s="9" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>29</v>
+      </c>
+      <c r="D14" s="9">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="15" ht="22.5" customHeight="1">
+      <c r="A15" s="9" t="s">
+        <v>30</v>
+      </c>
       <c r="B15" s="9" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>32</v>
+      </c>
+      <c r="D15" s="9">
+        <v>15.0</v>
+      </c>
+    </row>
+    <row r="16" ht="22.5" customHeight="1">
+      <c r="A16" s="9" t="s">
+        <v>33</v>
+      </c>
       <c r="B16" s="9" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>35</v>
+      </c>
+      <c r="D16" s="9">
+        <v>30.0</v>
+      </c>
+    </row>
+    <row r="17" ht="22.5" customHeight="1">
+      <c r="A17" s="9" t="s">
+        <v>36</v>
+      </c>
       <c r="B17" s="9" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>31</v>
+        <v>38</v>
+      </c>
+      <c r="D17" s="9">
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="18" ht="22.5" customHeight="1">
+      <c r="A18" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D18" s="9">
+        <v>20.0</v>
       </c>
     </row>
   </sheetData>
@@ -698,6 +1277,9 @@
     <hyperlink r:id="rId1" ref="B2"/>
   </hyperlinks>
   <drawing r:id="rId2"/>
+  <tableParts count="1">
+    <tablePart r:id="rId4"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -707,8 +1289,539 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
-  <sheetData/>
-  <drawing r:id="rId1"/>
+  <cols>
+    <col customWidth="1" min="3" max="3" width="14.13"/>
+    <col customWidth="1" min="4" max="4" width="23.63"/>
+    <col customWidth="1" min="5" max="5" width="22.75"/>
+    <col customWidth="1" min="6" max="6" width="22.88"/>
+    <col customWidth="1" min="7" max="7" width="17.63"/>
+    <col customWidth="1" min="8" max="8" width="13.88"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" s="15">
+        <v>46109.0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" s="16">
+        <v>46117.0</v>
+      </c>
+    </row>
+    <row r="5" ht="31.5" customHeight="1">
+      <c r="A5" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="G5" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="H5" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="I5" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="J5" s="20"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="20"/>
+      <c r="M5" s="20"/>
+      <c r="N5" s="20"/>
+      <c r="O5" s="20"/>
+      <c r="P5" s="20"/>
+      <c r="Q5" s="20"/>
+      <c r="R5" s="20"/>
+      <c r="S5" s="20"/>
+      <c r="T5" s="20"/>
+      <c r="U5" s="20"/>
+      <c r="V5" s="20"/>
+      <c r="W5" s="20"/>
+      <c r="X5" s="20"/>
+      <c r="Y5" s="20"/>
+      <c r="Z5" s="20"/>
+    </row>
+    <row r="6" ht="31.5" customHeight="1">
+      <c r="A6" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="J6" s="22"/>
+      <c r="K6" s="22"/>
+      <c r="L6" s="22"/>
+      <c r="M6" s="22"/>
+      <c r="N6" s="22"/>
+      <c r="O6" s="22"/>
+      <c r="P6" s="22"/>
+      <c r="Q6" s="22"/>
+      <c r="R6" s="22"/>
+      <c r="S6" s="22"/>
+      <c r="T6" s="22"/>
+      <c r="U6" s="22"/>
+      <c r="V6" s="22"/>
+      <c r="W6" s="22"/>
+      <c r="X6" s="22"/>
+      <c r="Y6" s="22"/>
+      <c r="Z6" s="22"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="23">
+        <v>1.0</v>
+      </c>
+      <c r="B7" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="D7" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="E7" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="F7" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="G7" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="H7" s="20"/>
+      <c r="I7" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="J7" s="20"/>
+      <c r="K7" s="20"/>
+      <c r="L7" s="20"/>
+      <c r="M7" s="20"/>
+      <c r="N7" s="20"/>
+      <c r="O7" s="20"/>
+      <c r="P7" s="20"/>
+      <c r="Q7" s="20"/>
+      <c r="R7" s="20"/>
+      <c r="S7" s="20"/>
+      <c r="T7" s="20"/>
+      <c r="U7" s="20"/>
+      <c r="V7" s="20"/>
+      <c r="W7" s="20"/>
+      <c r="X7" s="20"/>
+      <c r="Y7" s="20"/>
+      <c r="Z7" s="20"/>
+    </row>
+    <row r="8" ht="48.75" customHeight="1">
+      <c r="A8" s="28">
+        <v>2.0</v>
+      </c>
+      <c r="C8" s="29" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" ht="47.25" customHeight="1">
+      <c r="A9" s="29">
+        <v>3.0</v>
+      </c>
+      <c r="C9" s="29" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" ht="49.5" customHeight="1">
+      <c r="A10" s="29">
+        <v>4.0</v>
+      </c>
+      <c r="C10" s="29" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" ht="54.0" customHeight="1">
+      <c r="A11" s="29">
+        <v>5.0</v>
+      </c>
+      <c r="C11" s="29" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" ht="52.5" customHeight="1">
+      <c r="A12" s="29">
+        <v>6.0</v>
+      </c>
+      <c r="C12" s="29" t="s">
+        <v>66</v>
+      </c>
+      <c r="F12" s="29" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" ht="46.5" customHeight="1">
+      <c r="B13" s="30" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" ht="51.75" customHeight="1">
+      <c r="A14" s="29">
+        <v>7.0</v>
+      </c>
+      <c r="C14" s="28" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" ht="60.0" customHeight="1">
+      <c r="A15" s="29">
+        <v>8.0</v>
+      </c>
+      <c r="C15" s="28" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="16" ht="52.5" customHeight="1">
+      <c r="A16" s="29">
+        <v>9.0</v>
+      </c>
+      <c r="C16" s="28" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="17" ht="52.5" customHeight="1">
+      <c r="A17" s="29">
+        <v>10.0</v>
+      </c>
+      <c r="C17" s="30" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="18" ht="52.5" customHeight="1">
+      <c r="A18" s="31" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="19" ht="52.5" customHeight="1">
+      <c r="B19" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="D19" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="E19" s="29" t="s">
+        <v>76</v>
+      </c>
+      <c r="F19" s="29" t="s">
+        <v>77</v>
+      </c>
+      <c r="G19" s="29" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="20" ht="52.5" customHeight="1">
+      <c r="C20" s="29" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="21" ht="52.5" customHeight="1">
+      <c r="C21" s="29" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" ht="52.5" customHeight="1">
+      <c r="B22" s="29" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="23" ht="62.25" customHeight="1">
+      <c r="C23" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" s="29" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" ht="62.25" customHeight="1">
+      <c r="C24" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="D24" s="29" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="25" ht="62.25" customHeight="1">
+      <c r="C25" s="29" t="s">
+        <v>82</v>
+      </c>
+      <c r="D25" s="29" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="26" ht="62.25" customHeight="1">
+      <c r="C26" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="D26" s="29" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="27" ht="62.25" customHeight="1">
+      <c r="A27" s="31" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="28" ht="62.25" customHeight="1">
+      <c r="B28" s="29" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29" ht="62.25" customHeight="1">
+      <c r="C29" s="29" t="s">
+        <v>87</v>
+      </c>
+      <c r="D29" s="29" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" ht="62.25" customHeight="1">
+      <c r="C30" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="D30" s="29" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="31" ht="62.25" customHeight="1">
+      <c r="C31" s="29" t="s">
+        <v>91</v>
+      </c>
+      <c r="D31" s="29" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="32" ht="62.25" customHeight="1">
+      <c r="C32" s="29" t="s">
+        <v>93</v>
+      </c>
+      <c r="D32" s="29" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="33" ht="62.25" customHeight="1">
+      <c r="B33" s="29" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="34" ht="62.25" customHeight="1">
+      <c r="C34" s="29" t="s">
+        <v>95</v>
+      </c>
+      <c r="D34" s="29" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="35" ht="62.25" customHeight="1">
+      <c r="C35" s="29" t="s">
+        <v>70</v>
+      </c>
+      <c r="D35" s="29" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="36" ht="62.25" customHeight="1">
+      <c r="C36" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="D36" s="29" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="37" ht="62.25" customHeight="1">
+      <c r="A37" s="31" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" ht="62.25" customHeight="1">
+      <c r="B38" s="29" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="39" ht="62.25" customHeight="1">
+      <c r="C39" s="29" t="s">
+        <v>101</v>
+      </c>
+      <c r="D39" s="29" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="40" ht="62.25" customHeight="1">
+      <c r="C40" s="29" t="s">
+        <v>103</v>
+      </c>
+      <c r="D40" s="29" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="41" ht="62.25" customHeight="1">
+      <c r="C41" s="29" t="s">
+        <v>105</v>
+      </c>
+      <c r="D41" s="29" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="42" ht="62.25" customHeight="1">
+      <c r="B42" s="29" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="43" ht="62.25" customHeight="1">
+      <c r="C43" s="29" t="s">
+        <v>107</v>
+      </c>
+      <c r="D43" s="29" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="44" ht="62.25" customHeight="1">
+      <c r="C44" s="29" t="s">
+        <v>109</v>
+      </c>
+      <c r="D44" s="29" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="45" ht="62.25" customHeight="1">
+      <c r="C45" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="D45" s="29" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="46" ht="62.25" customHeight="1">
+      <c r="C46" s="29" t="s">
+        <v>111</v>
+      </c>
+      <c r="D46" s="29" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="47" ht="62.25" customHeight="1">
+      <c r="C47" s="29" t="s">
+        <v>114</v>
+      </c>
+      <c r="D47" s="29" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="48" ht="62.25" customHeight="1">
+      <c r="A48" s="28" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="49" ht="62.25" customHeight="1">
+      <c r="B49" s="29" t="s">
+        <v>117</v>
+      </c>
+      <c r="C49" s="29" t="s">
+        <v>118</v>
+      </c>
+      <c r="D49" s="29" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="50" ht="62.25" customHeight="1">
+      <c r="B50" s="33" t="s">
+        <v>68</v>
+      </c>
+      <c r="C50" s="29"/>
+      <c r="D50" s="29"/>
+    </row>
+    <row r="51" ht="62.25" customHeight="1">
+      <c r="B51" s="29"/>
+      <c r="C51" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="D51" s="29" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="52" ht="62.25" customHeight="1">
+      <c r="C52" s="29" t="s">
+        <v>122</v>
+      </c>
+      <c r="D52" s="29" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="53" ht="61.5" customHeight="1">
+      <c r="C53" s="29" t="s">
+        <v>124</v>
+      </c>
+      <c r="D53" s="29" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="54" ht="61.5" customHeight="1">
+      <c r="C54" s="29" t="s">
+        <v>126</v>
+      </c>
+      <c r="D54" s="29" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="55" ht="61.5" customHeight="1">
+      <c r="C55" s="29" t="s">
+        <v>128</v>
+      </c>
+      <c r="D55" s="29" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="56" ht="61.5" customHeight="1"/>
+    <row r="57" ht="61.5" customHeight="1"/>
+    <row r="58" ht="61.5" customHeight="1"/>
+    <row r="59" ht="61.5" customHeight="1"/>
+    <row r="60" ht="61.5" customHeight="1"/>
+    <row r="61" ht="61.5" customHeight="1"/>
+    <row r="62" ht="61.5" customHeight="1"/>
+    <row r="63" ht="61.5" customHeight="1"/>
+    <row r="64" ht="61.5" customHeight="1"/>
+    <row r="65" ht="61.5" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A6:I6"/>
+    <mergeCell ref="A18:I18"/>
+    <mergeCell ref="A27:I27"/>
+    <mergeCell ref="A37:I37"/>
+    <mergeCell ref="A48:I48"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink r:id="rId1" ref="B1"/>
+  </hyperlinks>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -720,8 +1833,8 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="s">
-        <v>32</v>
+      <c r="A1" s="29" t="s">
+        <v>130</v>
       </c>
     </row>
   </sheetData>
